--- a/scripts/2026양산철인3종대회_기록결과.xlsx
+++ b/scripts/2026양산철인3종대회_기록결과.xlsx
@@ -512,7 +512,22 @@
         <v>상위그룹 남</v>
       </c>
       <c r="E5" t="str">
-        <v>기록없음</v>
+        <v>02:10:07</v>
+      </c>
+      <c r="F5" t="str">
+        <v>00:21:28</v>
+      </c>
+      <c r="G5" t="str">
+        <v>00:01:44</v>
+      </c>
+      <c r="H5" t="str">
+        <v>01:02:36</v>
+      </c>
+      <c r="I5" t="str">
+        <v>00:01:08</v>
+      </c>
+      <c r="J5" t="str">
+        <v>00:43:11</v>
       </c>
     </row>
     <row r="6">
@@ -529,7 +544,22 @@
         <v>상위그룹 남</v>
       </c>
       <c r="E6" t="str">
-        <v>기록없음</v>
+        <v>02:01:23</v>
+      </c>
+      <c r="F6" t="str">
+        <v>00:20:49</v>
+      </c>
+      <c r="G6" t="str">
+        <v>00:01:28</v>
+      </c>
+      <c r="H6" t="str">
+        <v>01:00:01</v>
+      </c>
+      <c r="I6" t="str">
+        <v>00:00:56</v>
+      </c>
+      <c r="J6" t="str">
+        <v>00:38:09</v>
       </c>
     </row>
     <row r="7">
@@ -580,7 +610,22 @@
         <v>상위그룹 남</v>
       </c>
       <c r="E9" t="str">
-        <v>기록없음</v>
+        <v>02:15:11</v>
+      </c>
+      <c r="F9" t="str">
+        <v>00:31:31</v>
+      </c>
+      <c r="G9" t="str">
+        <v>00:02:05</v>
+      </c>
+      <c r="H9" t="str">
+        <v>00:58:56</v>
+      </c>
+      <c r="I9" t="str">
+        <v>00:01:28</v>
+      </c>
+      <c r="J9" t="str">
+        <v>00:41:12</v>
       </c>
     </row>
     <row r="10">
@@ -594,7 +639,22 @@
         <v>상위그룹 남</v>
       </c>
       <c r="E10" t="str">
-        <v>기록없음</v>
+        <v>02:07:57</v>
+      </c>
+      <c r="F10" t="str">
+        <v>00:21:24</v>
+      </c>
+      <c r="G10" t="str">
+        <v>00:01:18</v>
+      </c>
+      <c r="H10" t="str">
+        <v>01:03:08</v>
+      </c>
+      <c r="I10" t="str">
+        <v>00:01:03</v>
+      </c>
+      <c r="J10" t="str">
+        <v>00:41:04</v>
       </c>
     </row>
     <row r="11">
